--- a/scripts/DoAn4_Bemori/data/ai/TimKiem/data_TimKiem_ai.xlsx
+++ b/scripts/DoAn4_Bemori/data/ai/TimKiem/data_TimKiem_ai.xlsx
@@ -425,77 +425,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>folder</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>formats</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
           <t>keyword</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TimKiem</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>['json', 'csv', 'txt', 'xlsx', 'yaml']</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bông</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>laptop</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>12345</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>điện thoại</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>@#&amp;$%!</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>#discount2024!</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>gấu bông</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>giá trị$%^&amp;*()</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gấu Bông 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cảm hứng gấu bông</t>
         </is>
       </c>
     </row>
